--- a/AtchisonRegime/Outputs/Aust/ASX300_Communication/df_regTrendSummaryASX300_Communication.xlsx
+++ b/AtchisonRegime/Outputs/Aust/ASX300_Communication/df_regTrendSummaryASX300_Communication.xlsx
@@ -736,13 +736,13 @@
         <v>45351</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45747</v>
+        <v>45777</v>
       </c>
       <c r="E14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F14" t="n">
-        <v>0.06473491471119242</v>
+        <v>0.02878101938011102</v>
       </c>
     </row>
   </sheetData>
